--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -482,10 +492,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -519,10 +539,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -556,10 +586,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -593,10 +633,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -630,10 +680,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -667,10 +727,20 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -704,10 +774,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -736,22 +816,121 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Google Fit</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:28:49</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:07:38</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -766,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +961,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Total Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Total Points</t>
         </is>
       </c>
@@ -793,10 +977,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.74</v>
+        <v>26.57</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -811,6 +998,9 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -824,6 +1014,9 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -841,6 +1034,11 @@
           <t>---</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -849,10 +1047,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.27</v>
+        <v>44.1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -440,25 +440,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Image Link</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Image Link</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -492,20 +482,10 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -539,20 +519,10 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -586,20 +556,10 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -633,20 +593,10 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -680,20 +630,10 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -727,20 +667,10 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -774,20 +704,10 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -983,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1053,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,6 +849,53 @@
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5/21/2026 18:56:16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -897,7 +944,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.57</v>
+        <v>29.45</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -967,7 +1014,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.1</v>
+        <v>46.98</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,15 +440,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -457,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,19 +492,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -519,10 +539,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -531,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,12 +571,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -556,19 +586,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>5/21/2026 18:56:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -593,10 +633,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -605,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>5/23/2026 18:20:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -615,25 +665,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -642,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>2026-05-14 19:21:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,12 +712,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -679,7 +739,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:21</t>
+          <t>2026-05-14 19:59:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -694,7 +754,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -716,7 +776,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-16 14:00:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -726,12 +786,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -741,20 +801,10 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -763,7 +813,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-16 18:30:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -778,7 +828,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -788,20 +838,10 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -810,7 +850,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-17 09:37:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -820,12 +860,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,20 +875,10 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -857,7 +887,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5/21/2026 18:56:16</t>
+          <t>2026-05-17 15:41:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -867,35 +897,62 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:46:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Run/Jog</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -944,13 +1001,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.45</v>
+        <v>21.69</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -960,7 +1017,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -976,7 +1033,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1014,13 +1071,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.98</v>
+        <v>21.69</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-14 19:21:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,24 +482,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -507,14 +499,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-14 19:59:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,24 +521,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>View</t>
@@ -561,7 +545,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-16 14:00:21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,29 +555,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>View</t>
@@ -601,14 +577,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5/21/2026 18:56:16</t>
+          <t>2026-05-16 18:30:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,24 +599,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>View</t>
@@ -655,7 +623,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5/23/2026 18:20:55</t>
+          <t>2026-05-17 09:37:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -665,29 +633,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>View</t>
@@ -702,7 +662,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-17 15:41:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -712,25 +672,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Cycling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -739,7 +701,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-17 16:46:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -754,20 +716,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -776,7 +740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -786,12 +750,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -801,10 +765,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Flagged</t>
         </is>
@@ -813,7 +787,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -828,7 +802,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -838,10 +812,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -850,7 +834,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -860,12 +844,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -875,10 +859,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -887,7 +881,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>5/21/2026 18:56:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -897,12 +891,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -912,47 +906,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>View</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-05-17 16:46:21</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1001,13 +968,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.69</v>
+        <v>29.45</v>
       </c>
       <c r="C2" t="n">
-        <v>3390</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1017,7 +984,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1033,7 +1000,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1071,13 +1038,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.69</v>
+        <v>46.98</v>
       </c>
       <c r="C6" t="n">
-        <v>3390</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,7 +765,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5/21/2026 18:56:16</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -920,6 +920,53 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-23 18:20:55</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -968,13 +1015,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.45</v>
+        <v>36.89</v>
       </c>
       <c r="C2" t="n">
+        <v>3390</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1038,13 +1085,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.98</v>
+        <v>54.42</v>
       </c>
       <c r="C6" t="n">
+        <v>3390</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,16 +482,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>View</t>
@@ -499,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,16 +529,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>View</t>
@@ -545,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -555,21 +571,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>View</t>
@@ -577,14 +601,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -599,16 +623,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>View</t>
@@ -623,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -633,21 +665,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>View</t>
@@ -662,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>5/26/2026 14:21:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -672,21 +712,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1,889</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>View</t>
@@ -701,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17 16:46:21</t>
+          <t>2026-05-14 19:21:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -716,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -740,7 +788,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-14 19:59:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -755,24 +803,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.54</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>View</t>
@@ -780,14 +820,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-16 14:00:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -797,29 +837,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>View</t>
@@ -827,14 +859,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-16 18:30:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -849,24 +881,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.86</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>View</t>
@@ -881,7 +905,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-17 09:37:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -891,29 +915,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Run/Jog</t>
+          <t>Steps</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Strava</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>View</t>
@@ -928,7 +944,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-17 15:41:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -938,35 +954,66 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Cycling</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.78</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:46:21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Run/Jog</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>7.44</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3,390</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1050,7 +1097,7 @@
         <v>12.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1889</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1088,7 +1135,7 @@
         <v>54.42</v>
       </c>
       <c r="C6" t="n">
-        <v>3390</v>
+        <v>5279</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5/26/2026 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1,889</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,16 +764,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>View</t>
@@ -788,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -803,16 +811,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>View</t>
@@ -827,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -837,21 +853,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>View</t>
@@ -859,14 +883,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -881,16 +905,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>7.44</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3,390</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>View</t>
@@ -905,7 +937,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>6/1/2026 14:34:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -915,105 +947,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-05-17 15:41:15</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cycling</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-05-17 16:46:21</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1062,13 +1024,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.89</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1078,7 +1040,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1094,10 +1056,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1889</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1132,13 +1094,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.42</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>5279</v>
+        <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5/26/2026 14:21:27</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1,889</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-14 19:21:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,16 +764,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>7.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Google Fit</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>View</t>
@@ -788,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-14 19:59:35</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -803,16 +811,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>View</t>
@@ -827,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-16 14:00:21</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -837,21 +853,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>View</t>
@@ -859,14 +883,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-16 18:30:22</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -881,16 +905,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>7.07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>View</t>
@@ -905,7 +937,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17 09:37:57</t>
+          <t>2026-06-01 14:34:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -915,21 +947,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steps</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.29</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>10.97</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>View</t>
@@ -944,7 +984,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-17 15:41:15</t>
+          <t>2026-06-02 19:19:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -954,66 +994,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Run/Jog</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>7.23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-05-17 16:46:21</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1062,7 +1071,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.89</v>
+        <v>73.69</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
@@ -1078,7 +1087,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1094,10 +1103,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1889</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1132,10 +1141,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54.42</v>
+        <v>73.69</v>
       </c>
       <c r="C6" t="n">
-        <v>5279</v>
+        <v>3390</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,53 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6/3/2026 18:54:32</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
@@ -1071,13 +1118,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.69</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1141,13 +1188,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73.69</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1072,6 +1072,100 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>Flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6/4/2026 19:03:19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7.11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6/5/2026 18:50:18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -1118,13 +1212,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80.93000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1188,13 +1282,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80.93000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Committee Approval Required</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,53 @@
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6/6/2026 18:18:05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.34</v>
+        <v>102.8</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>95.34</v>
+        <v>102.8</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,6 +1211,53 @@
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6/7/2026 18:45:45</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Strava</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1259,7 +1306,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>102.8</v>
+        <v>110.18</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
@@ -1329,7 +1376,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.8</v>
+        <v>110.18</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1260,6 +1260,53 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6/9/2026 18:31:22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
         </is>
       </c>
     </row>
@@ -1306,13 +1353,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110.18</v>
+        <v>117.23</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1376,13 +1423,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.18</v>
+        <v>117.23</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,45 +1266,92 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>6/10/2026 18:07:46</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>6/9/2026 18:31:22</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>7.05</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
         </is>
@@ -1353,13 +1400,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117.23</v>
+        <v>120.87</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1423,13 +1470,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>117.23</v>
+        <v>120.87</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1313,45 +1313,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>6/11/2026 19:07:45</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10.09</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6/12/2026 8:57:56</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>6/9/2026 18:31:22</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>7.05</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
         </is>
@@ -1400,13 +1494,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>120.87</v>
+        <v>134.61</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1470,13 +1564,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120.87</v>
+        <v>134.61</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Members/Jeremy_Activity_Report.xlsx
+++ b/Reports/Members/Jeremy_Activity_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:21:27</t>
+          <t>2026-05-18 18:05:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,14 +507,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Flagged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-28 18:44:00</t>
+          <t>2026-05-19 17:28:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:41</t>
+          <t>2026-05-20 16:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-30 20:44:11</t>
+          <t>2026-05-21 18:56:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.56</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-31 20:24:34</t>
+          <t>2026-05-23 18:20:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,390</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Google Fit</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 18:05:56</t>
+          <t>2026-05-26 14:21:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Flagged</t>
+          <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-19 17:28:49</t>
+          <t>2026-05-28 18:44:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-20 16:07:38</t>
+          <t>2026-05-29 19:25:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-21 18:56:16</t>
+          <t>2026-05-30 20:44:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>8.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 18:20:55</t>
+          <t>2026-05-31 20:24:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3,390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Google Fit</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1360,7 +1360,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6/12/2026 8:57:56</t>
+          <t>6/12/2026 19:21:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1407,45 +1407,92 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>6/12/2026 8:57:56</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Committee Approval Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>6/9/2026 18:31:22</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Jeremy</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Run/Jog</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Run/Jog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>7.05</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Committee Approval Required</t>
         </is>
@@ -1494,13 +1541,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>134.61</v>
+        <v>142.05</v>
       </c>
       <c r="C2" t="n">
         <v>3390</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1564,13 +1611,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.61</v>
+        <v>142.05</v>
       </c>
       <c r="C6" t="n">
         <v>3390</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
